--- a/04_Figures/F05_classification/modules/T2/HR_LR/svm/c_data/results.xlsx
+++ b/04_Figures/F05_classification/modules/T2/HR_LR/svm/c_data/results.xlsx
@@ -524,13 +524,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.446428571428571</v>
+        <v>0.107142857142857</v>
       </c>
       <c r="I2" t="n">
-        <v>0.13069450138736</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.762162641469783</v>
+        <v>0.276550487641665</v>
       </c>
       <c r="K2"/>
       <c r="L2"/>
@@ -559,22 +559,22 @@
         <v>200</v>
       </c>
       <c r="H3" t="n">
-        <v>0.446428571428571</v>
+        <v>0.107142857142857</v>
       </c>
       <c r="I3" t="n">
-        <v>0.13069450138736</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.762162641469783</v>
+        <v>0.276550487641665</v>
       </c>
       <c r="K3" t="n">
-        <v>0.258706467661692</v>
+        <v>0.810945273631841</v>
       </c>
       <c r="L3" t="n">
-        <v>0.304196428571429</v>
+        <v>0.297410714285714</v>
       </c>
       <c r="M3" t="n">
-        <v>0.24079543705373</v>
+        <v>0.234170951326558</v>
       </c>
     </row>
   </sheetData>
@@ -601,7 +601,7 @@
         <v>15</v>
       </c>
       <c r="B2" t="n">
-        <v>0.321428571428571</v>
+        <v>0.196428571428571</v>
       </c>
     </row>
     <row r="3">
@@ -609,7 +609,7 @@
         <v>15</v>
       </c>
       <c r="B3" t="n">
-        <v>0.625</v>
+        <v>0.589285714285714</v>
       </c>
     </row>
     <row r="4">
@@ -617,7 +617,7 @@
         <v>15</v>
       </c>
       <c r="B4" t="n">
-        <v>0.25</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="5">
@@ -625,7 +625,7 @@
         <v>15</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0892857142857143</v>
+        <v>0.107142857142857</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         <v>15</v>
       </c>
       <c r="B7" t="n">
-        <v>0.392857142857143</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="8">
@@ -649,7 +649,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>0.625</v>
+        <v>0.553571428571428</v>
       </c>
     </row>
     <row r="9">
@@ -657,7 +657,7 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>0.321428571428571</v>
+        <v>0.232142857142857</v>
       </c>
     </row>
     <row r="10">
@@ -665,7 +665,7 @@
         <v>15</v>
       </c>
       <c r="B10" t="n">
-        <v>0.428571428571429</v>
+        <v>0.446428571428571</v>
       </c>
     </row>
     <row r="11">
@@ -673,7 +673,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>0.214285714285714</v>
+        <v>0.232142857142857</v>
       </c>
     </row>
     <row r="12">
@@ -681,7 +681,7 @@
         <v>15</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0357142857142857</v>
+        <v>0.196428571428571</v>
       </c>
     </row>
     <row r="13">
@@ -689,7 +689,7 @@
         <v>15</v>
       </c>
       <c r="B13" t="n">
-        <v>0.607142857142857</v>
+        <v>0.660714285714286</v>
       </c>
     </row>
     <row r="14">
@@ -705,7 +705,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="n">
-        <v>0.464285714285714</v>
+        <v>0.321428571428571</v>
       </c>
     </row>
     <row r="16">
@@ -713,7 +713,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.178571428571429</v>
+        <v>0.0535714285714286</v>
       </c>
     </row>
     <row r="17">
@@ -721,7 +721,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.285714285714286</v>
+        <v>0.178571428571429</v>
       </c>
     </row>
     <row r="18">
@@ -737,7 +737,7 @@
         <v>15</v>
       </c>
       <c r="B19" t="n">
-        <v>0.482142857142857</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="20">
@@ -745,7 +745,7 @@
         <v>15</v>
       </c>
       <c r="B20" t="n">
-        <v>0.107142857142857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -753,7 +753,7 @@
         <v>15</v>
       </c>
       <c r="B21" t="n">
-        <v>0.142857142857143</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="22">
@@ -761,7 +761,7 @@
         <v>15</v>
       </c>
       <c r="B22" t="n">
-        <v>0.232142857142857</v>
+        <v>0.107142857142857</v>
       </c>
     </row>
     <row r="23">
@@ -769,7 +769,7 @@
         <v>15</v>
       </c>
       <c r="B23" t="n">
-        <v>0.107142857142857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -777,7 +777,7 @@
         <v>15</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>0.0178571428571429</v>
       </c>
     </row>
     <row r="25">
@@ -785,7 +785,7 @@
         <v>15</v>
       </c>
       <c r="B25" t="n">
-        <v>0.446428571428571</v>
+        <v>0.357142857142857</v>
       </c>
     </row>
     <row r="26">
@@ -793,7 +793,7 @@
         <v>15</v>
       </c>
       <c r="B26" t="n">
-        <v>0.839285714285714</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="27">
@@ -801,7 +801,7 @@
         <v>15</v>
       </c>
       <c r="B27" t="n">
-        <v>0.821428571428571</v>
+        <v>0.732142857142857</v>
       </c>
     </row>
     <row r="28">
@@ -809,7 +809,7 @@
         <v>15</v>
       </c>
       <c r="B28" t="n">
-        <v>0.285714285714286</v>
+        <v>0.339285714285714</v>
       </c>
     </row>
     <row r="29">
@@ -817,7 +817,7 @@
         <v>15</v>
       </c>
       <c r="B29" t="n">
-        <v>0.267857142857143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -825,7 +825,7 @@
         <v>15</v>
       </c>
       <c r="B30" t="n">
-        <v>0.821428571428571</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="31">
@@ -833,7 +833,7 @@
         <v>15</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.107142857142857</v>
       </c>
     </row>
     <row r="32">
@@ -841,7 +841,7 @@
         <v>15</v>
       </c>
       <c r="B32" t="n">
-        <v>0.839285714285714</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="33">
@@ -849,7 +849,7 @@
         <v>15</v>
       </c>
       <c r="B33" t="n">
-        <v>0.767857142857143</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="34">
@@ -857,7 +857,7 @@
         <v>15</v>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>0.0178571428571429</v>
       </c>
     </row>
     <row r="35">
@@ -865,7 +865,7 @@
         <v>15</v>
       </c>
       <c r="B35" t="n">
-        <v>0.0892857142857143</v>
+        <v>0.107142857142857</v>
       </c>
     </row>
     <row r="36">
@@ -873,7 +873,7 @@
         <v>15</v>
       </c>
       <c r="B36" t="n">
-        <v>0.357142857142857</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="37">
@@ -881,7 +881,7 @@
         <v>15</v>
       </c>
       <c r="B37" t="n">
-        <v>0.0535714285714286</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="38">
@@ -889,7 +889,7 @@
         <v>15</v>
       </c>
       <c r="B38" t="n">
-        <v>0.392857142857143</v>
+        <v>0.267857142857143</v>
       </c>
     </row>
     <row r="39">
@@ -897,7 +897,7 @@
         <v>15</v>
       </c>
       <c r="B39" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0892857142857143</v>
       </c>
     </row>
     <row r="40">
@@ -905,7 +905,7 @@
         <v>15</v>
       </c>
       <c r="B40" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="41">
@@ -913,7 +913,7 @@
         <v>15</v>
       </c>
       <c r="B41" t="n">
-        <v>0.892857142857143</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="42">
@@ -921,7 +921,7 @@
         <v>15</v>
       </c>
       <c r="B42" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.160714285714286</v>
       </c>
     </row>
     <row r="43">
@@ -929,7 +929,7 @@
         <v>15</v>
       </c>
       <c r="B43" t="n">
-        <v>0.589285714285714</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="44">
@@ -945,7 +945,7 @@
         <v>15</v>
       </c>
       <c r="B45" t="n">
-        <v>0.178571428571429</v>
+        <v>0.0892857142857143</v>
       </c>
     </row>
     <row r="46">
@@ -953,7 +953,7 @@
         <v>15</v>
       </c>
       <c r="B46" t="n">
-        <v>0.142857142857143</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="47">
@@ -961,7 +961,7 @@
         <v>15</v>
       </c>
       <c r="B47" t="n">
-        <v>0.0892857142857143</v>
+        <v>0.178571428571429</v>
       </c>
     </row>
     <row r="48">
@@ -969,7 +969,7 @@
         <v>15</v>
       </c>
       <c r="B48" t="n">
-        <v>0.357142857142857</v>
+        <v>0.482142857142857</v>
       </c>
     </row>
     <row r="49">
@@ -977,7 +977,7 @@
         <v>15</v>
       </c>
       <c r="B49" t="n">
-        <v>0.214285714285714</v>
+        <v>0.232142857142857</v>
       </c>
     </row>
     <row r="50">
@@ -985,7 +985,7 @@
         <v>15</v>
       </c>
       <c r="B50" t="n">
-        <v>0.196428571428571</v>
+        <v>0.232142857142857</v>
       </c>
     </row>
     <row r="51">
@@ -993,7 +993,7 @@
         <v>15</v>
       </c>
       <c r="B51" t="n">
-        <v>0.303571428571429</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="52">
@@ -1001,7 +1001,7 @@
         <v>15</v>
       </c>
       <c r="B52" t="n">
-        <v>0.303571428571429</v>
+        <v>0.267857142857143</v>
       </c>
     </row>
     <row r="53">
@@ -1009,7 +1009,7 @@
         <v>15</v>
       </c>
       <c r="B53" t="n">
-        <v>0.232142857142857</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="54">
@@ -1017,7 +1017,7 @@
         <v>15</v>
       </c>
       <c r="B54" t="n">
-        <v>0.5</v>
+        <v>0.392857142857143</v>
       </c>
     </row>
     <row r="55">
@@ -1025,7 +1025,7 @@
         <v>15</v>
       </c>
       <c r="B55" t="n">
-        <v>0.0357142857142857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -1033,7 +1033,7 @@
         <v>15</v>
       </c>
       <c r="B56" t="n">
-        <v>0.214285714285714</v>
+        <v>0.232142857142857</v>
       </c>
     </row>
     <row r="57">
@@ -1041,7 +1041,7 @@
         <v>15</v>
       </c>
       <c r="B57" t="n">
-        <v>0.428571428571428</v>
+        <v>0.410714285714286</v>
       </c>
     </row>
     <row r="58">
@@ -1049,7 +1049,7 @@
         <v>15</v>
       </c>
       <c r="B58" t="n">
-        <v>0.25</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="59">
@@ -1057,7 +1057,7 @@
         <v>15</v>
       </c>
       <c r="B59" t="n">
-        <v>0.428571428571429</v>
+        <v>0.321428571428571</v>
       </c>
     </row>
     <row r="60">
@@ -1065,7 +1065,7 @@
         <v>15</v>
       </c>
       <c r="B60" t="n">
-        <v>0.375</v>
+        <v>0.482142857142857</v>
       </c>
     </row>
     <row r="61">
@@ -1073,7 +1073,7 @@
         <v>15</v>
       </c>
       <c r="B61" t="n">
-        <v>0.303571428571429</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="62">
@@ -1081,7 +1081,7 @@
         <v>15</v>
       </c>
       <c r="B62" t="n">
-        <v>0.482142857142857</v>
+        <v>0.464285714285714</v>
       </c>
     </row>
     <row r="63">
@@ -1089,7 +1089,7 @@
         <v>15</v>
       </c>
       <c r="B63" t="n">
-        <v>0.160714285714286</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="64">
@@ -1097,7 +1097,7 @@
         <v>15</v>
       </c>
       <c r="B64" t="n">
-        <v>0.660714285714286</v>
+        <v>0.767857142857143</v>
       </c>
     </row>
     <row r="65">
@@ -1105,7 +1105,7 @@
         <v>15</v>
       </c>
       <c r="B65" t="n">
-        <v>0.214285714285714</v>
+        <v>0.321428571428571</v>
       </c>
     </row>
     <row r="66">
@@ -1113,7 +1113,7 @@
         <v>15</v>
       </c>
       <c r="B66" t="n">
-        <v>0.357142857142857</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="67">
@@ -1121,7 +1121,7 @@
         <v>15</v>
       </c>
       <c r="B67" t="n">
-        <v>0.232142857142857</v>
+        <v>0.160714285714286</v>
       </c>
     </row>
     <row r="68">
@@ -1129,7 +1129,7 @@
         <v>15</v>
       </c>
       <c r="B68" t="n">
-        <v>0.160714285714286</v>
+        <v>0.196428571428571</v>
       </c>
     </row>
     <row r="69">
@@ -1137,7 +1137,7 @@
         <v>15</v>
       </c>
       <c r="B69" t="n">
-        <v>0.178571428571429</v>
+        <v>0.0535714285714286</v>
       </c>
     </row>
     <row r="70">
@@ -1145,7 +1145,7 @@
         <v>15</v>
       </c>
       <c r="B70" t="n">
-        <v>0.357142857142857</v>
+        <v>0.303571428571429</v>
       </c>
     </row>
     <row r="71">
@@ -1153,7 +1153,7 @@
         <v>15</v>
       </c>
       <c r="B71" t="n">
-        <v>0.107142857142857</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="72">
@@ -1161,7 +1161,7 @@
         <v>15</v>
       </c>
       <c r="B72" t="n">
-        <v>0.535714285714286</v>
+        <v>0.517857142857143</v>
       </c>
     </row>
     <row r="73">
@@ -1169,7 +1169,7 @@
         <v>15</v>
       </c>
       <c r="B73" t="n">
-        <v>0.0178571428571429</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1177,7 +1177,7 @@
         <v>15</v>
       </c>
       <c r="B74" t="n">
-        <v>0.178571428571429</v>
+        <v>0.232142857142857</v>
       </c>
     </row>
     <row r="75">
@@ -1185,7 +1185,7 @@
         <v>15</v>
       </c>
       <c r="B75" t="n">
-        <v>0.428571428571428</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="76">
@@ -1193,7 +1193,7 @@
         <v>15</v>
       </c>
       <c r="B76" t="n">
-        <v>0.357142857142857</v>
+        <v>0.303571428571428</v>
       </c>
     </row>
     <row r="77">
@@ -1201,7 +1201,7 @@
         <v>15</v>
       </c>
       <c r="B77" t="n">
-        <v>0.625</v>
+        <v>0.589285714285714</v>
       </c>
     </row>
     <row r="78">
@@ -1209,7 +1209,7 @@
         <v>15</v>
       </c>
       <c r="B78" t="n">
-        <v>0.732142857142857</v>
+        <v>0.696428571428572</v>
       </c>
     </row>
     <row r="79">
@@ -1217,7 +1217,7 @@
         <v>15</v>
       </c>
       <c r="B79" t="n">
-        <v>0.339285714285714</v>
+        <v>0.267857142857143</v>
       </c>
     </row>
     <row r="80">
@@ -1225,7 +1225,7 @@
         <v>15</v>
       </c>
       <c r="B80" t="n">
-        <v>0.0178571428571429</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="81">
@@ -1233,7 +1233,7 @@
         <v>15</v>
       </c>
       <c r="B81" t="n">
-        <v>0.357142857142857</v>
+        <v>0.267857142857143</v>
       </c>
     </row>
     <row r="82">
@@ -1241,7 +1241,7 @@
         <v>15</v>
       </c>
       <c r="B82" t="n">
-        <v>0.857142857142857</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="83">
@@ -1249,7 +1249,7 @@
         <v>15</v>
       </c>
       <c r="B83" t="n">
-        <v>0</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="84">
@@ -1257,7 +1257,7 @@
         <v>15</v>
       </c>
       <c r="B84" t="n">
-        <v>0</v>
+        <v>0.0892857142857143</v>
       </c>
     </row>
     <row r="85">
@@ -1265,7 +1265,7 @@
         <v>15</v>
       </c>
       <c r="B85" t="n">
-        <v>0</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="86">
@@ -1273,7 +1273,7 @@
         <v>15</v>
       </c>
       <c r="B86" t="n">
-        <v>0.232142857142857</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="87">
@@ -1281,7 +1281,7 @@
         <v>15</v>
       </c>
       <c r="B87" t="n">
-        <v>0.607142857142857</v>
+        <v>0.678571428571428</v>
       </c>
     </row>
     <row r="88">
@@ -1289,7 +1289,7 @@
         <v>15</v>
       </c>
       <c r="B88" t="n">
-        <v>0.339285714285714</v>
+        <v>0.357142857142857</v>
       </c>
     </row>
     <row r="89">
@@ -1297,7 +1297,7 @@
         <v>15</v>
       </c>
       <c r="B89" t="n">
-        <v>0.339285714285714</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="90">
@@ -1313,7 +1313,7 @@
         <v>15</v>
       </c>
       <c r="B91" t="n">
-        <v>0.339285714285714</v>
+        <v>0.446428571428571</v>
       </c>
     </row>
     <row r="92">
@@ -1321,7 +1321,7 @@
         <v>15</v>
       </c>
       <c r="B92" t="n">
-        <v>0.0535714285714286</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -1329,7 +1329,7 @@
         <v>15</v>
       </c>
       <c r="B93" t="n">
-        <v>0.107142857142857</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="94">
@@ -1337,7 +1337,7 @@
         <v>15</v>
       </c>
       <c r="B94" t="n">
-        <v>0.964285714285714</v>
+        <v>0.946428571428571</v>
       </c>
     </row>
     <row r="95">
@@ -1345,7 +1345,7 @@
         <v>15</v>
       </c>
       <c r="B95" t="n">
-        <v>0.696428571428571</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="96">
@@ -1353,7 +1353,7 @@
         <v>15</v>
       </c>
       <c r="B96" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.0892857142857143</v>
       </c>
     </row>
     <row r="97">
@@ -1361,7 +1361,7 @@
         <v>15</v>
       </c>
       <c r="B97" t="n">
-        <v>0.214285714285714</v>
+        <v>0.178571428571429</v>
       </c>
     </row>
     <row r="98">
@@ -1369,7 +1369,7 @@
         <v>15</v>
       </c>
       <c r="B98" t="n">
-        <v>0.428571428571429</v>
+        <v>0.428571428571428</v>
       </c>
     </row>
     <row r="99">
@@ -1377,7 +1377,7 @@
         <v>15</v>
       </c>
       <c r="B99" t="n">
-        <v>0.214285714285714</v>
+        <v>0.107142857142857</v>
       </c>
     </row>
     <row r="100">
@@ -1385,7 +1385,7 @@
         <v>15</v>
       </c>
       <c r="B100" t="n">
-        <v>0.142857142857143</v>
+        <v>0.107142857142857</v>
       </c>
     </row>
     <row r="101">
@@ -1393,7 +1393,7 @@
         <v>15</v>
       </c>
       <c r="B101" t="n">
-        <v>0.464285714285714</v>
+        <v>0.107142857142857</v>
       </c>
     </row>
     <row r="102">
@@ -1401,7 +1401,7 @@
         <v>15</v>
       </c>
       <c r="B102" t="n">
-        <v>0.410714285714286</v>
+        <v>0.428571428571428</v>
       </c>
     </row>
     <row r="103">
@@ -1409,7 +1409,7 @@
         <v>15</v>
       </c>
       <c r="B103" t="n">
-        <v>0.125</v>
+        <v>0.107142857142857</v>
       </c>
     </row>
     <row r="104">
@@ -1417,7 +1417,7 @@
         <v>15</v>
       </c>
       <c r="B104" t="n">
-        <v>0.339285714285714</v>
+        <v>0.553571428571429</v>
       </c>
     </row>
     <row r="105">
@@ -1425,7 +1425,7 @@
         <v>15</v>
       </c>
       <c r="B105" t="n">
-        <v>0.107142857142857</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="106">
@@ -1433,7 +1433,7 @@
         <v>15</v>
       </c>
       <c r="B106" t="n">
-        <v>0.428571428571428</v>
+        <v>0.321428571428571</v>
       </c>
     </row>
     <row r="107">
@@ -1441,7 +1441,7 @@
         <v>15</v>
       </c>
       <c r="B107" t="n">
-        <v>0</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="108">
@@ -1449,7 +1449,7 @@
         <v>15</v>
       </c>
       <c r="B108" t="n">
-        <v>0.321428571428571</v>
+        <v>0.392857142857143</v>
       </c>
     </row>
     <row r="109">
@@ -1457,7 +1457,7 @@
         <v>15</v>
       </c>
       <c r="B109" t="n">
-        <v>0.0357142857142857</v>
+        <v>0.0178571428571429</v>
       </c>
     </row>
     <row r="110">
@@ -1465,7 +1465,7 @@
         <v>15</v>
       </c>
       <c r="B110" t="n">
-        <v>0.392857142857143</v>
+        <v>0.357142857142857</v>
       </c>
     </row>
     <row r="111">
@@ -1473,7 +1473,7 @@
         <v>15</v>
       </c>
       <c r="B111" t="n">
-        <v>0.678571428571429</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="112">
@@ -1481,7 +1481,7 @@
         <v>15</v>
       </c>
       <c r="B112" t="n">
-        <v>0.125</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="113">
@@ -1489,7 +1489,7 @@
         <v>15</v>
       </c>
       <c r="B113" t="n">
-        <v>0.303571428571429</v>
+        <v>0.321428571428571</v>
       </c>
     </row>
     <row r="114">
@@ -1497,7 +1497,7 @@
         <v>15</v>
       </c>
       <c r="B114" t="n">
-        <v>0.303571428571429</v>
+        <v>0.196428571428571</v>
       </c>
     </row>
     <row r="115">
@@ -1505,7 +1505,7 @@
         <v>15</v>
       </c>
       <c r="B115" t="n">
-        <v>0.446428571428571</v>
+        <v>0.357142857142857</v>
       </c>
     </row>
     <row r="116">
@@ -1513,7 +1513,7 @@
         <v>15</v>
       </c>
       <c r="B116" t="n">
-        <v>0.196428571428571</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="117">
@@ -1521,7 +1521,7 @@
         <v>15</v>
       </c>
       <c r="B117" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.0357142857142857</v>
       </c>
     </row>
     <row r="118">
@@ -1529,7 +1529,7 @@
         <v>15</v>
       </c>
       <c r="B118" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="119">
@@ -1537,7 +1537,7 @@
         <v>15</v>
       </c>
       <c r="B119" t="n">
-        <v>0.160714285714286</v>
+        <v>0.232142857142857</v>
       </c>
     </row>
     <row r="120">
@@ -1553,7 +1553,7 @@
         <v>15</v>
       </c>
       <c r="B121" t="n">
-        <v>0.196428571428571</v>
+        <v>0.267857142857143</v>
       </c>
     </row>
     <row r="122">
@@ -1561,7 +1561,7 @@
         <v>15</v>
       </c>
       <c r="B122" t="n">
-        <v>0.589285714285714</v>
+        <v>0.446428571428571</v>
       </c>
     </row>
     <row r="123">
@@ -1569,7 +1569,7 @@
         <v>15</v>
       </c>
       <c r="B123" t="n">
-        <v>0.267857142857143</v>
+        <v>0.178571428571429</v>
       </c>
     </row>
     <row r="124">
@@ -1577,7 +1577,7 @@
         <v>15</v>
       </c>
       <c r="B124" t="n">
-        <v>0.232142857142857</v>
+        <v>0.107142857142857</v>
       </c>
     </row>
     <row r="125">
@@ -1585,7 +1585,7 @@
         <v>15</v>
       </c>
       <c r="B125" t="n">
-        <v>0.0892857142857143</v>
+        <v>0.107142857142857</v>
       </c>
     </row>
     <row r="126">
@@ -1593,7 +1593,7 @@
         <v>15</v>
       </c>
       <c r="B126" t="n">
-        <v>0.446428571428571</v>
+        <v>0.267857142857143</v>
       </c>
     </row>
     <row r="127">
@@ -1601,7 +1601,7 @@
         <v>15</v>
       </c>
       <c r="B127" t="n">
-        <v>0.178571428571429</v>
+        <v>0.0892857142857143</v>
       </c>
     </row>
     <row r="128">
@@ -1609,7 +1609,7 @@
         <v>15</v>
       </c>
       <c r="B128" t="n">
-        <v>0</v>
+        <v>0.160714285714286</v>
       </c>
     </row>
     <row r="129">
@@ -1617,7 +1617,7 @@
         <v>15</v>
       </c>
       <c r="B129" t="n">
-        <v>0.446428571428571</v>
+        <v>0.321428571428571</v>
       </c>
     </row>
     <row r="130">
@@ -1625,7 +1625,7 @@
         <v>15</v>
       </c>
       <c r="B130" t="n">
-        <v>0.571428571428572</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="131">
@@ -1633,7 +1633,7 @@
         <v>15</v>
       </c>
       <c r="B131" t="n">
-        <v>0.0178571428571429</v>
+        <v>0.107142857142857</v>
       </c>
     </row>
     <row r="132">
@@ -1641,7 +1641,7 @@
         <v>15</v>
       </c>
       <c r="B132" t="n">
-        <v>0.142857142857143</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="133">
@@ -1649,7 +1649,7 @@
         <v>15</v>
       </c>
       <c r="B133" t="n">
-        <v>0.732142857142857</v>
+        <v>0.678571428571429</v>
       </c>
     </row>
     <row r="134">
@@ -1657,7 +1657,7 @@
         <v>15</v>
       </c>
       <c r="B134" t="n">
-        <v>0.232142857142857</v>
+        <v>0.303571428571429</v>
       </c>
     </row>
     <row r="135">
@@ -1665,7 +1665,7 @@
         <v>15</v>
       </c>
       <c r="B135" t="n">
-        <v>0.303571428571428</v>
+        <v>0.303571428571429</v>
       </c>
     </row>
     <row r="136">
@@ -1673,7 +1673,7 @@
         <v>15</v>
       </c>
       <c r="B136" t="n">
-        <v>0.0892857142857143</v>
+        <v>0.0357142857142857</v>
       </c>
     </row>
     <row r="137">
@@ -1681,7 +1681,7 @@
         <v>15</v>
       </c>
       <c r="B137" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.0892857142857143</v>
       </c>
     </row>
     <row r="138">
@@ -1689,7 +1689,7 @@
         <v>15</v>
       </c>
       <c r="B138" t="n">
-        <v>0.482142857142857</v>
+        <v>0.589285714285714</v>
       </c>
     </row>
     <row r="139">
@@ -1697,7 +1697,7 @@
         <v>15</v>
       </c>
       <c r="B139" t="n">
-        <v>0.821428571428572</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="140">
@@ -1705,7 +1705,7 @@
         <v>15</v>
       </c>
       <c r="B140" t="n">
-        <v>0.482142857142857</v>
+        <v>0.446428571428571</v>
       </c>
     </row>
     <row r="141">
@@ -1713,7 +1713,7 @@
         <v>15</v>
       </c>
       <c r="B141" t="n">
-        <v>0.25</v>
+        <v>0.0178571428571429</v>
       </c>
     </row>
     <row r="142">
@@ -1721,7 +1721,7 @@
         <v>15</v>
       </c>
       <c r="B142" t="n">
-        <v>0.732142857142857</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="143">
@@ -1729,7 +1729,7 @@
         <v>15</v>
       </c>
       <c r="B143" t="n">
-        <v>0.482142857142857</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="144">
@@ -1737,7 +1737,7 @@
         <v>15</v>
       </c>
       <c r="B144" t="n">
-        <v>0.5</v>
+        <v>0.357142857142857</v>
       </c>
     </row>
     <row r="145">
@@ -1745,7 +1745,7 @@
         <v>15</v>
       </c>
       <c r="B145" t="n">
-        <v>0.303571428571429</v>
+        <v>0.178571428571429</v>
       </c>
     </row>
     <row r="146">
@@ -1753,7 +1753,7 @@
         <v>15</v>
       </c>
       <c r="B146" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.196428571428571</v>
       </c>
     </row>
     <row r="147">
@@ -1761,7 +1761,7 @@
         <v>15</v>
       </c>
       <c r="B147" t="n">
-        <v>0.25</v>
+        <v>0.339285714285714</v>
       </c>
     </row>
     <row r="148">
@@ -1769,7 +1769,7 @@
         <v>15</v>
       </c>
       <c r="B148" t="n">
-        <v>0.375</v>
+        <v>0.303571428571429</v>
       </c>
     </row>
     <row r="149">
@@ -1777,7 +1777,7 @@
         <v>15</v>
       </c>
       <c r="B149" t="n">
-        <v>0.0357142857142857</v>
+        <v>0.178571428571429</v>
       </c>
     </row>
     <row r="150">
@@ -1785,7 +1785,7 @@
         <v>15</v>
       </c>
       <c r="B150" t="n">
-        <v>0.160714285714286</v>
+        <v>0.303571428571429</v>
       </c>
     </row>
     <row r="151">
@@ -1793,7 +1793,7 @@
         <v>15</v>
       </c>
       <c r="B151" t="n">
-        <v>0.267857142857143</v>
+        <v>0.160714285714286</v>
       </c>
     </row>
     <row r="152">
@@ -1801,7 +1801,7 @@
         <v>15</v>
       </c>
       <c r="B152" t="n">
-        <v>0.160714285714286</v>
+        <v>0.0892857142857143</v>
       </c>
     </row>
     <row r="153">
@@ -1809,7 +1809,7 @@
         <v>15</v>
       </c>
       <c r="B153" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.232142857142857</v>
       </c>
     </row>
     <row r="154">
@@ -1817,7 +1817,7 @@
         <v>15</v>
       </c>
       <c r="B154" t="n">
-        <v>0</v>
+        <v>0.0535714285714286</v>
       </c>
     </row>
     <row r="155">
@@ -1825,7 +1825,7 @@
         <v>15</v>
       </c>
       <c r="B155" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.0892857142857143</v>
       </c>
     </row>
     <row r="156">
@@ -1833,7 +1833,7 @@
         <v>15</v>
       </c>
       <c r="B156" t="n">
-        <v>0.196428571428571</v>
+        <v>0.267857142857143</v>
       </c>
     </row>
     <row r="157">
@@ -1841,7 +1841,7 @@
         <v>15</v>
       </c>
       <c r="B157" t="n">
-        <v>0.607142857142857</v>
+        <v>0.660714285714286</v>
       </c>
     </row>
     <row r="158">
@@ -1849,7 +1849,7 @@
         <v>15</v>
       </c>
       <c r="B158" t="n">
-        <v>0.357142857142857</v>
+        <v>0.196428571428571</v>
       </c>
     </row>
     <row r="159">
@@ -1857,7 +1857,7 @@
         <v>15</v>
       </c>
       <c r="B159" t="n">
-        <v>0.928571428571429</v>
+        <v>0.946428571428571</v>
       </c>
     </row>
     <row r="160">
@@ -1865,7 +1865,7 @@
         <v>15</v>
       </c>
       <c r="B160" t="n">
-        <v>0.642857142857143</v>
+        <v>0.589285714285714</v>
       </c>
     </row>
     <row r="161">
@@ -1873,7 +1873,7 @@
         <v>15</v>
       </c>
       <c r="B161" t="n">
-        <v>0.785714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="162">
@@ -1881,7 +1881,7 @@
         <v>15</v>
       </c>
       <c r="B162" t="n">
-        <v>0.571428571428571</v>
+        <v>0.428571428571428</v>
       </c>
     </row>
     <row r="163">
@@ -1889,7 +1889,7 @@
         <v>15</v>
       </c>
       <c r="B163" t="n">
-        <v>0.125</v>
+        <v>0.0892857142857143</v>
       </c>
     </row>
     <row r="164">
@@ -1897,7 +1897,7 @@
         <v>15</v>
       </c>
       <c r="B164" t="n">
-        <v>0</v>
+        <v>0.160714285714286</v>
       </c>
     </row>
     <row r="165">
@@ -1905,7 +1905,7 @@
         <v>15</v>
       </c>
       <c r="B165" t="n">
-        <v>0.410714285714286</v>
+        <v>0.267857142857143</v>
       </c>
     </row>
     <row r="166">
@@ -1913,7 +1913,7 @@
         <v>15</v>
       </c>
       <c r="B166" t="n">
-        <v>0.0892857142857143</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="167">
@@ -1921,7 +1921,7 @@
         <v>15</v>
       </c>
       <c r="B167" t="n">
-        <v>0.160714285714286</v>
+        <v>0.0892857142857143</v>
       </c>
     </row>
     <row r="168">
@@ -1929,7 +1929,7 @@
         <v>15</v>
       </c>
       <c r="B168" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="169">
@@ -1937,7 +1937,7 @@
         <v>15</v>
       </c>
       <c r="B169" t="n">
-        <v>0.142857142857143</v>
+        <v>0.267857142857143</v>
       </c>
     </row>
     <row r="170">
@@ -1953,7 +1953,7 @@
         <v>15</v>
       </c>
       <c r="B171" t="n">
-        <v>0.446428571428571</v>
+        <v>0.303571428571429</v>
       </c>
     </row>
     <row r="172">
@@ -1961,7 +1961,7 @@
         <v>15</v>
       </c>
       <c r="B172" t="n">
-        <v>0.660714285714286</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="173">
@@ -1977,7 +1977,7 @@
         <v>15</v>
       </c>
       <c r="B174" t="n">
-        <v>0.125</v>
+        <v>0.178571428571429</v>
       </c>
     </row>
     <row r="175">
@@ -1985,7 +1985,7 @@
         <v>15</v>
       </c>
       <c r="B175" t="n">
-        <v>0.285714285714286</v>
+        <v>0.232142857142857</v>
       </c>
     </row>
     <row r="176">
@@ -1993,7 +1993,7 @@
         <v>15</v>
       </c>
       <c r="B176" t="n">
-        <v>0.160714285714286</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="177">
@@ -2001,7 +2001,7 @@
         <v>15</v>
       </c>
       <c r="B177" t="n">
-        <v>0.107142857142857</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="178">
@@ -2009,7 +2009,7 @@
         <v>15</v>
       </c>
       <c r="B178" t="n">
-        <v>0.625</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="179">
@@ -2017,7 +2017,7 @@
         <v>15</v>
       </c>
       <c r="B179" t="n">
-        <v>0.714285714285714</v>
+        <v>0.732142857142857</v>
       </c>
     </row>
     <row r="180">
@@ -2041,7 +2041,7 @@
         <v>15</v>
       </c>
       <c r="B182" t="n">
-        <v>0.732142857142857</v>
+        <v>0.607142857142857</v>
       </c>
     </row>
     <row r="183">
@@ -2049,7 +2049,7 @@
         <v>15</v>
       </c>
       <c r="B183" t="n">
-        <v>0.142857142857143</v>
+        <v>0.232142857142857</v>
       </c>
     </row>
     <row r="184">
@@ -2057,7 +2057,7 @@
         <v>15</v>
       </c>
       <c r="B184" t="n">
-        <v>0.0178571428571429</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="185">
@@ -2065,7 +2065,7 @@
         <v>15</v>
       </c>
       <c r="B185" t="n">
-        <v>0.767857142857143</v>
+        <v>0.821428571428571</v>
       </c>
     </row>
     <row r="186">
@@ -2073,7 +2073,7 @@
         <v>15</v>
       </c>
       <c r="B186" t="n">
-        <v>0.125</v>
+        <v>0.303571428571428</v>
       </c>
     </row>
     <row r="187">
@@ -2081,7 +2081,7 @@
         <v>15</v>
       </c>
       <c r="B187" t="n">
-        <v>0.178571428571429</v>
+        <v>0.107142857142857</v>
       </c>
     </row>
     <row r="188">
@@ -2089,7 +2089,7 @@
         <v>15</v>
       </c>
       <c r="B188" t="n">
-        <v>0.107142857142857</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="189">
@@ -2097,7 +2097,7 @@
         <v>15</v>
       </c>
       <c r="B189" t="n">
-        <v>0.696428571428572</v>
+        <v>0.678571428571429</v>
       </c>
     </row>
     <row r="190">
@@ -2105,7 +2105,7 @@
         <v>15</v>
       </c>
       <c r="B190" t="n">
-        <v>0.0357142857142857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
@@ -2113,7 +2113,7 @@
         <v>15</v>
       </c>
       <c r="B191" t="n">
-        <v>0.428571428571428</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="192">
@@ -2121,7 +2121,7 @@
         <v>15</v>
       </c>
       <c r="B192" t="n">
-        <v>0.0178571428571429</v>
+        <v>0.0892857142857143</v>
       </c>
     </row>
     <row r="193">
@@ -2129,7 +2129,7 @@
         <v>15</v>
       </c>
       <c r="B193" t="n">
-        <v>0.178571428571429</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="194">
@@ -2137,7 +2137,7 @@
         <v>15</v>
       </c>
       <c r="B194" t="n">
-        <v>0.464285714285714</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="195">
@@ -2145,7 +2145,7 @@
         <v>15</v>
       </c>
       <c r="B195" t="n">
-        <v>0.0178571428571429</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="196">
@@ -2153,7 +2153,7 @@
         <v>15</v>
       </c>
       <c r="B196" t="n">
-        <v>0.392857142857143</v>
+        <v>0.464285714285714</v>
       </c>
     </row>
     <row r="197">
@@ -2161,7 +2161,7 @@
         <v>15</v>
       </c>
       <c r="B197" t="n">
-        <v>0.107142857142857</v>
+        <v>0.357142857142857</v>
       </c>
     </row>
     <row r="198">
@@ -2169,7 +2169,7 @@
         <v>15</v>
       </c>
       <c r="B198" t="n">
-        <v>0.785714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="199">
@@ -2177,7 +2177,7 @@
         <v>15</v>
       </c>
       <c r="B199" t="n">
-        <v>0.428571428571429</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="200">
@@ -2185,7 +2185,7 @@
         <v>15</v>
       </c>
       <c r="B200" t="n">
-        <v>0.267857142857143</v>
+        <v>0.607142857142857</v>
       </c>
     </row>
     <row r="201">
@@ -2193,7 +2193,7 @@
         <v>15</v>
       </c>
       <c r="B201" t="n">
-        <v>0.410714285714286</v>
+        <v>0.267857142857143</v>
       </c>
     </row>
   </sheetData>
@@ -2232,7 +2232,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.358650915681178</v>
+        <v>0.411124500329144</v>
       </c>
     </row>
     <row r="3">
@@ -2246,7 +2246,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.48268930060005</v>
+        <v>0.44578898662279</v>
       </c>
     </row>
     <row r="4">
@@ -2260,7 +2260,7 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.38087858209904</v>
+        <v>0.38191866453004</v>
       </c>
     </row>
     <row r="5">
@@ -2274,7 +2274,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.440929283445373</v>
+        <v>0.439954325241014</v>
       </c>
     </row>
     <row r="6">
@@ -2288,7 +2288,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.528376120712274</v>
+        <v>0.467405549432414</v>
       </c>
     </row>
     <row r="7">
@@ -2302,7 +2302,7 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.516952493872642</v>
+        <v>0.443934805449688</v>
       </c>
     </row>
     <row r="8">
@@ -2316,7 +2316,7 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.361125855739274</v>
+        <v>0.336541865942835</v>
       </c>
     </row>
     <row r="9">
@@ -2330,7 +2330,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.330030309236338</v>
+        <v>0.447160354897217</v>
       </c>
     </row>
     <row r="10">
@@ -2344,7 +2344,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.508075350182107</v>
+        <v>0.565111079883695</v>
       </c>
     </row>
     <row r="11">
@@ -2358,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.365196406262436</v>
+        <v>0.454433092902901</v>
       </c>
     </row>
     <row r="12">
@@ -2372,7 +2372,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.406430322672234</v>
+        <v>0.484392724939982</v>
       </c>
     </row>
     <row r="13">
@@ -2386,7 +2386,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.410899111350826</v>
+        <v>0.552371531798428</v>
       </c>
     </row>
     <row r="14">
@@ -2400,7 +2400,7 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.96967415765928</v>
+        <v>0.746508181224393</v>
       </c>
     </row>
     <row r="15">
@@ -2414,7 +2414,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.540882858299035</v>
+        <v>0.512388488730579</v>
       </c>
     </row>
     <row r="16">
@@ -2428,7 +2428,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.48143459925335</v>
+        <v>0.416082631989914</v>
       </c>
     </row>
   </sheetData>
